--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEB9C54-E2B2-4F41-8343-97F315CE8833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B96995F-BE31-46B5-8C5B-2FE5E8FCA69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -423,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -435,51 +438,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -510,6 +468,55 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -826,35 +833,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="F2" s="20" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35"/>
+      <c r="F2" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="22"/>
-      <c r="K2" s="23" t="s">
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="38"/>
+      <c r="K2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="25"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="41"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -867,11 +874,11 @@
       <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="26"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="6" t="s">
@@ -880,11 +887,11 @@
       <c r="I3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="11"/>
       <c r="K3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="6" t="s">
@@ -894,11 +901,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="19">
         <v>0.05</v>
       </c>
       <c r="C4" s="2">
@@ -909,10 +916,10 @@
         <v>0.48</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="23">
         <v>0.1</v>
       </c>
       <c r="H4" s="3"/>
@@ -921,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="8"/>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="19">
         <v>0.15</v>
       </c>
       <c r="M4" s="10"/>
@@ -933,23 +940,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="43">
         <v>0.1</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
         <f t="shared" ref="D5:D10" si="0">+B5*C5</f>
         <v>0</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="21">
         <v>0.1</v>
       </c>
       <c r="H5" s="3"/>
@@ -958,23 +965,23 @@
         <v>0</v>
       </c>
       <c r="J5" s="8"/>
-      <c r="K5" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="36">
+      <c r="K5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="21">
         <v>0.15</v>
       </c>
-      <c r="M5" s="28"/>
+      <c r="M5" s="13"/>
       <c r="N5" s="3">
         <f t="shared" ref="N5:N10" si="2">+L5*M5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="23">
         <v>0.1</v>
       </c>
       <c r="C6" s="3"/>
@@ -983,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="38">
+      <c r="F6" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="23">
         <v>0.15</v>
       </c>
       <c r="H6" s="3"/>
@@ -995,23 +1002,23 @@
         <v>0</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="23">
         <v>0.05</v>
       </c>
-      <c r="M6" s="28"/>
+      <c r="M6" s="13"/>
       <c r="N6" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="21">
         <v>0.15</v>
       </c>
       <c r="C7" s="3"/>
@@ -1020,10 +1027,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="21">
         <v>0.1</v>
       </c>
       <c r="H7" s="3"/>
@@ -1032,23 +1039,23 @@
         <v>0</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="21">
         <v>0.2</v>
       </c>
-      <c r="M7" s="28"/>
+      <c r="M7" s="13"/>
       <c r="N7" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="23">
         <v>0.1</v>
       </c>
       <c r="C8" s="3"/>
@@ -1057,35 +1064,35 @@
         <v>0</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="23">
         <v>0.15</v>
       </c>
-      <c r="H8" s="29"/>
+      <c r="H8" s="14"/>
       <c r="I8" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="23">
         <v>0.1</v>
       </c>
-      <c r="M8" s="28"/>
+      <c r="M8" s="13"/>
       <c r="N8" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="21">
         <v>0.25</v>
       </c>
       <c r="C9" s="3"/>
@@ -1094,22 +1101,22 @@
         <v>0</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="21">
         <v>0.15</v>
       </c>
-      <c r="H9" s="29"/>
+      <c r="H9" s="14"/>
       <c r="I9" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="21">
         <v>0.15</v>
       </c>
       <c r="M9" s="3"/>
@@ -1118,11 +1125,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="38">
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="23">
         <v>0.25</v>
       </c>
       <c r="C10" s="3"/>
@@ -1131,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="23">
         <v>0.1</v>
       </c>
-      <c r="H10" s="29"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="38">
+      <c r="L10" s="23">
         <v>0.2</v>
       </c>
       <c r="M10" s="3"/>
@@ -1155,19 +1162,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
-      <c r="B11" s="30"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="32">
+      <c r="D11" s="17">
         <f>SUM(D4:D10)</f>
         <v>0.48</v>
       </c>
       <c r="E11" s="8"/>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="21">
         <v>0.15</v>
       </c>
       <c r="H11" s="3"/>
@@ -1179,12 +1186,12 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="32">
+      <c r="N11" s="17">
         <f>SUM(N4:N10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1193,7 +1200,7 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="32">
+      <c r="I12" s="17">
         <f>SUM(I4:I11)</f>
         <v>0</v>
       </c>
@@ -1203,7 +1210,7 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1219,7 +1226,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1235,7 +1242,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1251,7 +1258,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1267,31 +1274,31 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="29"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="16"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="32"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -1300,11 +1307,11 @@
       <c r="D18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="26"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="G18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="6" t="s">
@@ -1313,29 +1320,31 @@
       <c r="I18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-    </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="19">
         <v>0.05</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
+      <c r="C19" s="2">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2">
         <f>+B19*C19</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="8"/>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="19">
         <v>0.1</v>
       </c>
       <c r="H19" s="2"/>
@@ -1349,23 +1358,25 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="36">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="43">
         <v>0.1</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3">
+      <c r="C20" s="2">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2">
         <f t="shared" ref="D20:D27" si="3">+B20*C20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="23">
         <v>0.15</v>
       </c>
       <c r="H20" s="3"/>
@@ -1379,23 +1390,23 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="37" t="s">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="23">
         <v>0.2</v>
       </c>
-      <c r="C21" s="28"/>
+      <c r="C21" s="13"/>
       <c r="D21" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="36">
+      <c r="F21" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="21">
         <v>0.1</v>
       </c>
       <c r="H21" s="3"/>
@@ -1409,26 +1420,26 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="21">
         <v>0.2</v>
       </c>
-      <c r="C22" s="31"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="23">
         <v>0.15</v>
       </c>
-      <c r="H22" s="29"/>
+      <c r="H22" s="14"/>
       <c r="I22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1439,11 +1450,11 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="38">
+      <c r="B23" s="23">
         <v>0.05</v>
       </c>
       <c r="C23" s="3"/>
@@ -1452,13 +1463,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="8"/>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="21">
         <v>0.1</v>
       </c>
-      <c r="H23" s="29"/>
+      <c r="H23" s="14"/>
       <c r="I23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1469,26 +1480,26 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="24">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C24" s="31"/>
+      <c r="C24" s="16"/>
       <c r="D24" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E24" s="8"/>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="23">
         <v>0.1</v>
       </c>
-      <c r="H24" s="29"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1499,26 +1510,26 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37" t="s">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="40">
+      <c r="B25" s="25">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C25" s="41"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E25" s="8"/>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="21">
         <v>0.1</v>
       </c>
-      <c r="H25" s="41"/>
+      <c r="H25" s="26"/>
       <c r="I25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1529,11 +1540,11 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="35" t="s">
+    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="36">
+      <c r="B26" s="21">
         <v>0.2</v>
       </c>
       <c r="C26" s="3"/>
@@ -1542,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="8"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="38">
+      <c r="G26" s="23">
         <v>0.2</v>
       </c>
       <c r="H26" s="3"/>
@@ -1559,11 +1570,11 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="38">
+      <c r="B27" s="23">
         <v>0.05</v>
       </c>
       <c r="C27" s="3"/>
@@ -1572,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="8"/>
-      <c r="I27" s="32">
+      <c r="I27" s="17">
         <f>SUM(I19:I26)</f>
         <v>0</v>
       </c>
@@ -1582,10 +1593,10 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D28" s="32">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D28" s="17">
         <f>SUM(D19:D27)</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B96995F-BE31-46B5-8C5B-2FE5E8FCA69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC57612-1120-4AFE-B068-2E6F3100DD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -468,54 +468,54 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -842,24 +842,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
-      <c r="F2" s="36" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="F2" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="38"/>
-      <c r="K2" s="39" t="s">
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="40"/>
+      <c r="K2" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="41"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="43"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -941,10 +941,10 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="28">
         <v>0.1</v>
       </c>
       <c r="C5" s="2"/>
@@ -965,16 +965,18 @@
         <v>0</v>
       </c>
       <c r="J5" s="8"/>
-      <c r="K5" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="21">
+      <c r="K5" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="28">
         <v>0.15</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="3">
+      <c r="M5" s="10">
+        <v>6</v>
+      </c>
+      <c r="N5" s="2">
         <f t="shared" ref="N5:N10" si="2">+L5*M5</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -1188,7 +1190,7 @@
       <c r="M11" s="8"/>
       <c r="N11" s="17">
         <f>SUM(N4:N10)</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1275,19 +1277,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="32"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="34"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1359,10 +1361,10 @@
       <c r="N19" s="8"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="43">
+      <c r="A20" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="28">
         <v>0.1</v>
       </c>
       <c r="C20" s="2">

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC57612-1120-4AFE-B068-2E6F3100DD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D950189-ABEC-44AD-8E92-2C732CD932B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -148,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +216,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -426,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -517,6 +522,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,15 +843,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>12</v>
       </c>
@@ -861,7 +871,7 @@
       <c r="M2" s="42"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -901,7 +911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
@@ -934,13 +944,15 @@
       <c r="L4" s="19">
         <v>0.15</v>
       </c>
-      <c r="M4" s="10"/>
+      <c r="M4" s="10">
+        <v>0</v>
+      </c>
       <c r="N4" s="2">
         <f>+L4*M4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
@@ -953,14 +965,14 @@
         <v>0</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="28">
         <v>0.1</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2">
         <f t="shared" ref="I5:I11" si="1">+G5*H5</f>
         <v>0</v>
       </c>
@@ -979,27 +991,27 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="45">
         <v>0.1</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3">
+      <c r="C6" s="46"/>
+      <c r="D6" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23">
+      <c r="F6" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="45">
         <v>0.15</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3">
+      <c r="H6" s="46"/>
+      <c r="I6" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1010,13 +1022,15 @@
       <c r="L6" s="23">
         <v>0.05</v>
       </c>
-      <c r="M6" s="13"/>
+      <c r="M6" s="13">
+        <v>0</v>
+      </c>
       <c r="N6" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>11</v>
       </c>
@@ -1047,13 +1061,15 @@
       <c r="L7" s="21">
         <v>0.2</v>
       </c>
-      <c r="M7" s="13"/>
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
       <c r="N7" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>19</v>
       </c>
@@ -1084,13 +1100,15 @@
       <c r="L8" s="23">
         <v>0.1</v>
       </c>
-      <c r="M8" s="13"/>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
       <c r="N8" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
@@ -1121,13 +1139,15 @@
       <c r="L9" s="21">
         <v>0.15</v>
       </c>
-      <c r="M9" s="3"/>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
       <c r="N9" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>0</v>
       </c>
@@ -1158,13 +1178,15 @@
       <c r="L10" s="23">
         <v>0.2</v>
       </c>
-      <c r="M10" s="3"/>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
       <c r="N10" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="15"/>
       <c r="C11" s="9"/>
@@ -1193,7 +1215,7 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1212,7 +1234,7 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1228,7 +1250,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1244,7 +1266,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1260,7 +1282,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1276,7 +1298,7 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="29" t="s">
         <v>15</v>
       </c>
@@ -1296,7 +1318,7 @@
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -1328,7 +1350,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
@@ -1360,7 +1382,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -1375,14 +1397,14 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="45">
         <v>0.15</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3">
+      <c r="H20" s="46"/>
+      <c r="I20" s="46">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>0</v>
       </c>
@@ -1392,7 +1414,7 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>7</v>
       </c>
@@ -1422,7 +1444,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
@@ -1452,7 +1474,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
@@ -1482,7 +1504,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>25</v>
       </c>
@@ -1512,7 +1534,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>26</v>
       </c>
@@ -1542,7 +1564,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
@@ -1572,7 +1594,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>28</v>
       </c>
@@ -1595,7 +1617,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D28" s="17">
         <f>SUM(D19:D27)</f>
         <v>1.5</v>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D950189-ABEC-44AD-8E92-2C732CD932B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A44F46-F6E5-4814-8782-B833901EEB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -477,56 +480,56 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,35 +846,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
-      <c r="F2" s="38" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="40"/>
+      <c r="F2" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="40"/>
-      <c r="K2" s="41" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43"/>
+      <c r="K2" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="43"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="46"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -911,7 +914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
@@ -952,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
@@ -991,29 +994,31 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="30">
         <v>0.1</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46">
+      <c r="C6" s="31"/>
+      <c r="D6" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="45">
+      <c r="F6" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="19">
         <v>0.15</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46">
+      <c r="H6" s="2">
+        <v>7.69</v>
+      </c>
+      <c r="I6" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1535</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="22" t="s">
@@ -1030,7 +1035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>11</v>
       </c>
@@ -1069,7 +1074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>19</v>
       </c>
@@ -1108,7 +1113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
@@ -1147,7 +1152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>0</v>
       </c>
@@ -1186,7 +1191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="15"/>
       <c r="C11" s="9"/>
@@ -1215,7 +1220,7 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1226,7 +1231,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="17">
         <f>SUM(I4:I11)</f>
-        <v>0</v>
+        <v>1.1535</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1234,7 +1239,7 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1250,7 +1255,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1266,7 +1271,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1282,7 +1287,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1298,27 +1303,27 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="29" t="s">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="34"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -1350,7 +1355,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
@@ -1382,7 +1387,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -1397,14 +1402,14 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="45">
+      <c r="G20" s="30">
         <v>0.15</v>
       </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46">
+      <c r="H20" s="31"/>
+      <c r="I20" s="31">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>0</v>
       </c>
@@ -1414,7 +1419,7 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>7</v>
       </c>
@@ -1444,7 +1449,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
@@ -1474,7 +1479,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
@@ -1504,7 +1509,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>25</v>
       </c>
@@ -1534,7 +1539,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>26</v>
       </c>
@@ -1564,7 +1569,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
@@ -1594,7 +1599,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>28</v>
       </c>
@@ -1617,7 +1622,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D28" s="17">
         <f>SUM(D19:D27)</f>
         <v>1.5</v>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A44F46-F6E5-4814-8782-B833901EEB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675B592D-2331-40EA-9B22-2C4084FB4D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -148,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +224,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -434,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -529,6 +542,16 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -846,15 +869,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
         <v>12</v>
       </c>
@@ -874,7 +897,7 @@
       <c r="M2" s="45"/>
       <c r="N2" s="46"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -914,7 +937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
@@ -948,14 +971,14 @@
         <v>0.15</v>
       </c>
       <c r="M4" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N4" s="2">
         <f>+L4*M4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1.3499999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
@@ -994,15 +1017,15 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="48">
         <v>0.1</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31">
+      <c r="C6" s="49"/>
+      <c r="D6" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1014,11 +1037,11 @@
         <v>0.15</v>
       </c>
       <c r="H6" s="2">
-        <v>7.69</v>
+        <v>7.66</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="1"/>
-        <v>1.1535</v>
+        <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="22" t="s">
@@ -1035,27 +1058,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="52">
         <v>0.15</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
+      <c r="C7" s="31"/>
+      <c r="D7" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="52">
         <v>0.1</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3">
+      <c r="H7" s="31"/>
+      <c r="I7" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1074,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>19</v>
       </c>
@@ -1113,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
@@ -1152,7 +1175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>0</v>
       </c>
@@ -1191,7 +1214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="15"/>
       <c r="C11" s="9"/>
@@ -1217,10 +1240,10 @@
       <c r="M11" s="8"/>
       <c r="N11" s="17">
         <f>SUM(N4:N10)</f>
-        <v>0.89999999999999991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1231,7 +1254,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="17">
         <f>SUM(I4:I11)</f>
-        <v>1.1535</v>
+        <v>1.149</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1239,7 +1262,7 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1255,7 +1278,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1271,7 +1294,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1287,7 +1310,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1303,7 +1326,7 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="32" t="s">
         <v>15</v>
       </c>
@@ -1323,7 +1346,7 @@
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -1355,7 +1378,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
@@ -1387,7 +1410,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -1402,14 +1425,14 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="48">
         <v>0.15</v>
       </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31">
+      <c r="H20" s="49"/>
+      <c r="I20" s="49">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>0</v>
       </c>
@@ -1419,27 +1442,27 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="30">
         <v>0.2</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="3">
+      <c r="C21" s="50"/>
+      <c r="D21" s="31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="21">
+      <c r="F21" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="52">
         <v>0.1</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3">
+      <c r="H21" s="31"/>
+      <c r="I21" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1449,7 +1472,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
@@ -1479,7 +1502,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
@@ -1509,7 +1532,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>25</v>
       </c>
@@ -1539,7 +1562,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>26</v>
       </c>
@@ -1569,7 +1592,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
@@ -1599,7 +1622,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>28</v>
       </c>
@@ -1622,7 +1645,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D28" s="17">
         <f>SUM(D19:D27)</f>
         <v>1.5</v>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675B592D-2331-40EA-9B22-2C4084FB4D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FB2968-5CF0-45EF-A296-0E99D9F1EEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -447,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -498,60 +501,63 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -869,35 +875,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="40"/>
-      <c r="F2" s="41" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="F2" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-      <c r="K2" s="44" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="48"/>
+      <c r="K2" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="46"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -937,7 +943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
@@ -952,16 +958,18 @@
         <v>0.48</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="19">
         <v>0.1</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
+      <c r="H4" s="2">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2">
         <f>+G4*H4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="18" t="s">
@@ -978,17 +986,19 @@
         <v>1.3499999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="28">
         <v>0.1</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2">
+        <v>10</v>
+      </c>
       <c r="D5" s="2">
         <f t="shared" ref="D5:D10" si="0">+B5*C5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="27" t="s">
@@ -997,10 +1007,12 @@
       <c r="G5" s="28">
         <v>0.1</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2">
+        <v>9</v>
+      </c>
       <c r="I5" s="2">
         <f t="shared" ref="I5:I11" si="1">+G5*H5</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="27" t="s">
@@ -1017,17 +1029,19 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="48">
+      <c r="B6" s="33">
         <v>0.1</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49">
+      <c r="C6" s="34">
+        <v>10</v>
+      </c>
+      <c r="D6" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="18" t="s">
@@ -1058,11 +1072,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="51" t="s">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="36">
         <v>0.15</v>
       </c>
       <c r="C7" s="31"/>
@@ -1071,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="36">
         <v>0.1</v>
       </c>
       <c r="H7" s="31"/>
@@ -1097,7 +1111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>19</v>
       </c>
@@ -1136,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
@@ -1175,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>0</v>
       </c>
@@ -1214,13 +1228,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="15"/>
       <c r="C11" s="9"/>
       <c r="D11" s="17">
         <f>SUM(D4:D10)</f>
-        <v>0.48</v>
+        <v>2.48</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="20" t="s">
@@ -1243,7 +1257,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1254,7 +1268,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="17">
         <f>SUM(I4:I11)</f>
-        <v>1.149</v>
+        <v>3.0489999999999999</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1262,7 +1276,7 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1278,7 +1292,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1294,7 +1308,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1310,7 +1324,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1326,27 +1340,27 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="32" t="s">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -1378,7 +1392,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
@@ -1399,10 +1413,12 @@
       <c r="G19" s="19">
         <v>0.1</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2">
+        <v>10</v>
+      </c>
       <c r="I19" s="2">
         <f>+G19*H19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
@@ -1410,7 +1426,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -1425,14 +1441,14 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="33">
         <v>0.15</v>
       </c>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49">
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>0</v>
       </c>
@@ -1442,23 +1458,25 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="33">
         <v>0.2</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="31">
+      <c r="C21" s="52">
+        <v>8.4</v>
+      </c>
+      <c r="D21" s="34">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="52">
+      <c r="F21" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="36">
         <v>0.1</v>
       </c>
       <c r="H21" s="31"/>
@@ -1472,7 +1490,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
@@ -1485,14 +1503,14 @@
         <v>0</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="30">
         <v>0.15</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="3">
+      <c r="H22" s="53"/>
+      <c r="I22" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1502,7 +1520,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
@@ -1532,7 +1550,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>25</v>
       </c>
@@ -1562,7 +1580,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>26</v>
       </c>
@@ -1592,7 +1610,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
@@ -1622,7 +1640,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>28</v>
       </c>
@@ -1637,7 +1655,7 @@
       <c r="E27" s="8"/>
       <c r="I27" s="17">
         <f>SUM(I19:I26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -1645,10 +1663,10 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D28" s="17">
         <f>SUM(D19:D27)</f>
-        <v>1.5</v>
+        <v>3.18</v>
       </c>
     </row>
   </sheetData>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675B592D-2331-40EA-9B22-2C4084FB4D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB601FD-2327-4CFA-BD09-0C41145B8BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -219,14 +219,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -236,6 +228,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -447,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -493,11 +492,13 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -543,14 +544,16 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -878,24 +881,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="40"/>
-      <c r="F2" s="41" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="F2" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-      <c r="K2" s="44" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="45"/>
+      <c r="K2" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="46"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="48"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -952,16 +955,18 @@
         <v>0.48</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="19">
         <v>0.1</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
+      <c r="H4" s="2">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2">
         <f>+G4*H4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="18" t="s">
@@ -985,10 +990,12 @@
       <c r="B5" s="28">
         <v>0.1</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2">
+        <v>10</v>
+      </c>
       <c r="D5" s="2">
         <f t="shared" ref="D5:D10" si="0">+B5*C5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="27" t="s">
@@ -997,10 +1004,12 @@
       <c r="G5" s="28">
         <v>0.1</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2">
+        <v>9</v>
+      </c>
       <c r="I5" s="2">
         <f t="shared" ref="I5:I11" si="1">+G5*H5</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="27" t="s">
@@ -1018,16 +1027,18 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="48">
+      <c r="B6" s="31">
         <v>0.1</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49">
+      <c r="C6" s="32">
+        <v>10</v>
+      </c>
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="18" t="s">
@@ -1044,41 +1055,41 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="54">
         <v>0.05</v>
       </c>
-      <c r="M6" s="13">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
+      <c r="M6" s="33">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="50">
         <v>0.15</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31">
+      <c r="C7" s="32"/>
+      <c r="D7" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="50">
         <v>0.1</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31">
+      <c r="H7" s="32"/>
+      <c r="I7" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1220,7 +1231,7 @@
       <c r="C11" s="9"/>
       <c r="D11" s="17">
         <f>SUM(D4:D10)</f>
-        <v>0.48</v>
+        <v>2.48</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="20" t="s">
@@ -1254,7 +1265,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="17">
         <f>SUM(I4:I11)</f>
-        <v>1.149</v>
+        <v>3.0489999999999999</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1327,19 +1338,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="36"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1399,10 +1410,12 @@
       <c r="G19" s="19">
         <v>0.1</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2">
+        <v>10</v>
+      </c>
       <c r="I19" s="2">
         <f>+G19*H19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
@@ -1425,14 +1438,14 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="31">
         <v>0.15</v>
       </c>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49">
+      <c r="H20" s="32"/>
+      <c r="I20" s="32">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>0</v>
       </c>
@@ -1443,26 +1456,26 @@
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <v>0.2</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="31">
+      <c r="C21" s="51"/>
+      <c r="D21" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="52">
+      <c r="F21" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="50">
         <v>0.1</v>
       </c>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31">
+      <c r="H21" s="32"/>
+      <c r="I21" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1485,14 +1498,14 @@
         <v>0</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="19">
         <v>0.15</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="3">
+      <c r="H22" s="52"/>
+      <c r="I22" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1637,7 +1650,7 @@
       <c r="E27" s="8"/>
       <c r="I27" s="17">
         <f>SUM(I19:I26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FB2968-5CF0-45EF-A296-0E99D9F1EEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37B75B4-224C-4B8F-962C-3549552C33FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -450,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -510,53 +507,61 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -875,35 +880,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="F2" s="46" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="F2" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="48"/>
-      <c r="K2" s="49" t="s">
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="50"/>
+      <c r="K2" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="51"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="53"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -943,7 +948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
@@ -986,7 +991,7 @@
         <v>1.3499999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
@@ -1029,7 +1034,7 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
         <v>18</v>
       </c>
@@ -1058,41 +1063,41 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="30">
         <v>0.05</v>
       </c>
-      <c r="M6" s="13">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
+      <c r="M6" s="56">
+        <v>0</v>
+      </c>
+      <c r="N6" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="55">
         <v>0.15</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31">
+      <c r="C7" s="34"/>
+      <c r="D7" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="55">
         <v>0.1</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31">
+      <c r="H7" s="34"/>
+      <c r="I7" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1111,7 +1116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>19</v>
       </c>
@@ -1150,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
@@ -1189,7 +1194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="15"/>
       <c r="C11" s="9"/>
@@ -1257,7 +1262,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1276,7 +1281,7 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1292,7 +1297,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1308,7 +1313,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1324,7 +1329,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1340,27 +1345,27 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="37" t="s">
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="44"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -1392,7 +1397,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
@@ -1426,7 +1431,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -1458,14 +1463,14 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="33">
         <v>0.2</v>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="37">
         <v>8.4</v>
       </c>
       <c r="D21" s="34">
@@ -1473,14 +1478,14 @@
         <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="36">
+      <c r="F21" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55">
         <v>0.1</v>
       </c>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31">
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1490,7 +1495,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
@@ -1503,14 +1508,14 @@
         <v>0</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="33">
         <v>0.15</v>
       </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="31">
+      <c r="H22" s="57"/>
+      <c r="I22" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1520,7 +1525,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
@@ -1533,14 +1538,14 @@
         <v>0</v>
       </c>
       <c r="E23" s="8"/>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="36">
         <v>0.1</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="3">
+      <c r="H23" s="38"/>
+      <c r="I23" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1550,7 +1555,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>25</v>
       </c>
@@ -1580,7 +1585,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>26</v>
       </c>
@@ -1610,7 +1615,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
@@ -1640,7 +1645,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>28</v>
       </c>
@@ -1663,7 +1668,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D28" s="17">
         <f>SUM(D19:D27)</f>
         <v>3.18</v>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37B75B4-224C-4B8F-962C-3549552C33FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF0D6CE-6986-46D4-874F-EB2CCFCFDD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -145,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +240,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -447,7 +454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -511,51 +518,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -563,6 +525,55 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -889,24 +900,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
-      <c r="F2" s="48" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
+      <c r="F2" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="50"/>
-      <c r="K2" s="51" t="s">
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="54"/>
+      <c r="K2" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="53"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="57"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1063,25 +1074,25 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="33">
         <v>0.05</v>
       </c>
-      <c r="M6" s="56">
-        <v>0</v>
-      </c>
-      <c r="N6" s="31">
+      <c r="M6" s="37">
+        <v>0</v>
+      </c>
+      <c r="N6" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="40">
         <v>0.15</v>
       </c>
       <c r="C7" s="34"/>
@@ -1090,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="40">
         <v>0.1</v>
       </c>
       <c r="H7" s="34"/>
@@ -1102,41 +1113,41 @@
         <v>0</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="36">
         <v>0.2</v>
       </c>
-      <c r="M7" s="13">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
+      <c r="M7" s="41">
+        <v>0</v>
+      </c>
+      <c r="N7" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="30">
         <v>0.1</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="59">
         <v>0.15</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="3">
+      <c r="H8" s="38"/>
+      <c r="I8" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1346,19 +1357,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="41"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="48"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1478,10 +1489,10 @@
         <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55">
+      <c r="F21" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="40">
         <v>0.1</v>
       </c>
       <c r="H21" s="34"/>
@@ -1514,7 +1525,7 @@
       <c r="G22" s="33">
         <v>0.15</v>
       </c>
-      <c r="H22" s="57"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="34">
         <f t="shared" si="4"/>
         <v>0</v>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF0D6CE-6986-46D4-874F-EB2CCFCFDD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313CADCF-2954-4A1F-A661-963204924CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -145,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,14 +213,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -454,7 +449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -500,32 +495,27 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -570,10 +560,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -891,35 +877,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="49" t="s">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
-      <c r="F2" s="52" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
+      <c r="F2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="54"/>
-      <c r="K2" s="55" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="51"/>
+      <c r="K2" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="57"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="54"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -959,7 +945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
@@ -1002,7 +988,7 @@
         <v>1.3499999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
@@ -1045,17 +1031,17 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="31">
         <v>0.1</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="32">
         <v>10</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1074,43 +1060,47 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="31">
         <v>0.05</v>
       </c>
-      <c r="M6" s="37">
-        <v>0</v>
-      </c>
-      <c r="N6" s="34">
+      <c r="M6" s="33">
+        <v>0</v>
+      </c>
+      <c r="N6" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="36">
         <v>0.15</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34">
+      <c r="C7" s="32">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D7" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="36">
         <v>0.1</v>
       </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34">
+      <c r="H7" s="32">
+        <v>10</v>
+      </c>
+      <c r="I7" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="35" t="s">
@@ -1119,35 +1109,35 @@
       <c r="L7" s="36">
         <v>0.2</v>
       </c>
-      <c r="M7" s="41">
-        <v>0</v>
-      </c>
-      <c r="N7" s="31">
+      <c r="M7" s="33">
+        <v>0</v>
+      </c>
+      <c r="N7" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>0.1</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31">
+      <c r="C8" s="32"/>
+      <c r="D8" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="39">
         <v>0.15</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="31">
+      <c r="H8" s="34"/>
+      <c r="I8" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1166,7 +1156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
@@ -1205,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>0</v>
       </c>
@@ -1244,13 +1234,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="15"/>
       <c r="C11" s="9"/>
       <c r="D11" s="17">
         <f>SUM(D4:D10)</f>
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="20" t="s">
@@ -1273,7 +1263,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1284,7 +1274,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="17">
         <f>SUM(I4:I11)</f>
-        <v>3.0489999999999999</v>
+        <v>4.0489999999999995</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1292,7 +1282,7 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1308,7 +1298,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1324,7 +1314,7 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1340,7 +1330,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1356,27 +1346,27 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="43" t="s">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="45"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -1408,7 +1398,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
@@ -1442,7 +1432,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -1457,16 +1447,18 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="31">
         <v>0.15</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34">
+      <c r="H20" s="32">
+        <v>10</v>
+      </c>
+      <c r="I20" s="32">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
@@ -1474,31 +1466,33 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32" t="s">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="31">
         <v>0.2</v>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="33">
         <v>8.4</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="32">
         <f t="shared" si="3"/>
         <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="40">
+      <c r="F21" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="36">
         <v>0.1</v>
       </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34">
+      <c r="H21" s="32">
+        <v>8.52</v>
+      </c>
+      <c r="I21" s="32">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
@@ -1506,7 +1500,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
@@ -1519,14 +1513,14 @@
         <v>0</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="32" t="s">
+      <c r="F22" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="31">
         <v>0.15</v>
       </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="34">
+      <c r="H22" s="37"/>
+      <c r="I22" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1536,7 +1530,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
@@ -1555,8 +1549,8 @@
       <c r="G23" s="36">
         <v>0.1</v>
       </c>
-      <c r="H23" s="38"/>
-      <c r="I23" s="31">
+      <c r="H23" s="37"/>
+      <c r="I23" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1566,7 +1560,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>25</v>
       </c>
@@ -1596,7 +1590,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>26</v>
       </c>
@@ -1626,7 +1620,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
@@ -1656,7 +1650,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>28</v>
       </c>
@@ -1671,7 +1665,7 @@
       <c r="E27" s="8"/>
       <c r="I27" s="17">
         <f>SUM(I19:I26)</f>
-        <v>1</v>
+        <v>3.3519999999999999</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -1679,7 +1673,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D28" s="17">
         <f>SUM(D19:D27)</f>
         <v>3.18</v>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313CADCF-2954-4A1F-A661-963204924CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31388445-2142-4B59-9FF0-6B5636898D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -238,6 +235,7 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -449,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -463,7 +461,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -512,55 +509,59 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -886,24 +887,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
-      <c r="F2" s="49" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="F2" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51"/>
-      <c r="K2" s="52" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="48"/>
+      <c r="K2" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="54"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -946,10 +947,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>0.05</v>
       </c>
       <c r="C4" s="2">
@@ -960,10 +961,10 @@
         <v>0.48</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="18">
         <v>0.1</v>
       </c>
       <c r="H4" s="2">
@@ -974,10 +975,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="8"/>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="18">
         <v>0.15</v>
       </c>
       <c r="M4" s="10">
@@ -989,10 +990,10 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>0.1</v>
       </c>
       <c r="C5" s="2">
@@ -1003,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <v>0.1</v>
       </c>
       <c r="H5" s="2">
@@ -1017,10 +1018,10 @@
         <v>0.9</v>
       </c>
       <c r="J5" s="8"/>
-      <c r="K5" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="28">
+      <c r="K5" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="27">
         <v>0.15</v>
       </c>
       <c r="M5" s="10">
@@ -1032,24 +1033,24 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>0.1</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="31">
         <v>10</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="F6" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18">
         <v>0.15</v>
       </c>
       <c r="H6" s="2">
@@ -1060,107 +1061,105 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="30">
         <v>0.05</v>
       </c>
-      <c r="M6" s="33">
-        <v>0</v>
-      </c>
-      <c r="N6" s="32">
+      <c r="M6" s="32"/>
+      <c r="N6" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="35">
         <v>0.15</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="31">
         <v>9.8000000000000007</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="31">
         <f t="shared" si="0"/>
         <v>1.47</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="35">
         <v>0.1</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="31">
         <v>10</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="35">
         <v>0.2</v>
       </c>
-      <c r="M7" s="33">
-        <v>0</v>
-      </c>
-      <c r="N7" s="32">
+      <c r="M7" s="32"/>
+      <c r="N7" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>0.1</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32">
+      <c r="C8" s="31">
+        <v>7.4</v>
+      </c>
+      <c r="D8" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7400000000000001</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="30">
         <v>0.15</v>
       </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="29">
+      <c r="H8" s="36"/>
+      <c r="I8" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="54">
         <v>0.1</v>
       </c>
-      <c r="M8" s="13">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="M8" s="55">
+        <v>0</v>
+      </c>
+      <c r="N8" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <v>0.25</v>
       </c>
       <c r="C9" s="3"/>
@@ -1169,22 +1168,22 @@
         <v>0</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="20">
         <v>0.15</v>
       </c>
-      <c r="H9" s="14"/>
+      <c r="H9" s="13"/>
       <c r="I9" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="20">
         <v>0.15</v>
       </c>
       <c r="M9" s="3">
@@ -1196,10 +1195,10 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="A10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="22">
         <v>0.25</v>
       </c>
       <c r="C10" s="3"/>
@@ -1208,22 +1207,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="22">
         <v>0.1</v>
       </c>
-      <c r="H10" s="14"/>
+      <c r="H10" s="13"/>
       <c r="I10" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="22">
         <v>0.2</v>
       </c>
       <c r="M10" s="3">
@@ -1236,17 +1235,17 @@
     </row>
     <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
-      <c r="B11" s="15"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <f>SUM(D4:D10)</f>
-        <v>3.95</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="E11" s="8"/>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="20">
         <v>0.15</v>
       </c>
       <c r="H11" s="3"/>
@@ -1258,7 +1257,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="17">
+      <c r="N11" s="16">
         <f>SUM(N4:N10)</f>
         <v>2.25</v>
       </c>
@@ -1272,7 +1271,7 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="17">
+      <c r="I12" s="16">
         <f>SUM(I4:I11)</f>
         <v>4.0489999999999995</v>
       </c>
@@ -1347,19 +1346,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1399,10 +1398,10 @@
       <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <v>0.05</v>
       </c>
       <c r="C19" s="2">
@@ -1413,10 +1412,10 @@
         <v>0.5</v>
       </c>
       <c r="E19" s="8"/>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="18">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
@@ -1433,10 +1432,10 @@
       <c r="N19" s="8"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="28">
+      <c r="A20" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="27">
         <v>0.1</v>
       </c>
       <c r="C20" s="2">
@@ -1447,16 +1446,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="30">
         <v>0.15</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="31">
         <v>10</v>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="31">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>1.5</v>
       </c>
@@ -1467,30 +1466,30 @@
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>0.2</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="32">
         <v>8.4</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="31">
         <f t="shared" si="3"/>
         <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="36">
+      <c r="F21" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35">
         <v>0.1</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="31">
         <v>8.52</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="31">
         <f t="shared" si="4"/>
         <v>0.85199999999999998</v>
       </c>
@@ -1501,26 +1500,26 @@
       <c r="N21" s="8"/>
     </row>
     <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="27">
         <v>0.2</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="3">
+      <c r="C22" s="52"/>
+      <c r="D22" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="30">
         <v>0.15</v>
       </c>
-      <c r="H22" s="37"/>
-      <c r="I22" s="32">
+      <c r="H22" s="36"/>
+      <c r="I22" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1531,26 +1530,26 @@
       <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="54">
         <v>0.05</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3">
+      <c r="C23" s="28"/>
+      <c r="D23" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E23" s="8"/>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="35">
         <v>0.1</v>
       </c>
-      <c r="H23" s="37"/>
-      <c r="I23" s="32">
+      <c r="H23" s="36"/>
+      <c r="I23" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1561,26 +1560,26 @@
       <c r="N23" s="8"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="23">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C24" s="16"/>
+      <c r="C24" s="15"/>
       <c r="D24" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E24" s="8"/>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="54">
         <v>0.1</v>
       </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="3">
+      <c r="H24" s="33"/>
+      <c r="I24" s="28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1591,25 +1590,25 @@
       <c r="N24" s="8"/>
     </row>
     <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="24">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C25" s="26"/>
+      <c r="C25" s="25"/>
       <c r="D25" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E25" s="8"/>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="20">
         <v>0.1</v>
       </c>
-      <c r="H25" s="26"/>
+      <c r="H25" s="25"/>
       <c r="I25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1621,10 +1620,10 @@
       <c r="N25" s="8"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <v>0.2</v>
       </c>
       <c r="C26" s="3"/>
@@ -1633,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="8"/>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="22">
         <v>0.2</v>
       </c>
       <c r="H26" s="3"/>
@@ -1651,10 +1650,10 @@
       <c r="N26" s="8"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="22">
         <v>0.05</v>
       </c>
       <c r="C27" s="3"/>
@@ -1663,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="8"/>
-      <c r="I27" s="17">
+      <c r="I27" s="16">
         <f>SUM(I19:I26)</f>
         <v>3.3519999999999999</v>
       </c>
@@ -1674,7 +1673,7 @@
       <c r="N27" s="8"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D28" s="17">
+      <c r="D28" s="16">
         <f>SUM(D19:D27)</f>
         <v>3.18</v>
       </c>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31388445-2142-4B59-9FF0-6B5636898D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4699C9-F66D-48E1-9481-AC07CAB84031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -447,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -509,51 +512,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -561,7 +519,51 @@
     <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -887,24 +889,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="F2" s="46" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
+      <c r="F2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="48"/>
-      <c r="K2" s="49" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="51"/>
+      <c r="K2" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="51"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="54"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1141,18 +1143,18 @@
         <v>0</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="53" t="s">
+      <c r="K8" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="54">
+      <c r="L8" s="30">
         <v>0.1</v>
       </c>
-      <c r="M8" s="55">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="M8" s="32">
+        <v>5.2</v>
+      </c>
+      <c r="N8" s="31">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -1259,7 +1261,7 @@
       <c r="M11" s="8"/>
       <c r="N11" s="16">
         <f>SUM(N4:N10)</f>
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1346,19 +1348,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1506,7 +1508,7 @@
       <c r="B22" s="27">
         <v>0.2</v>
       </c>
-      <c r="C22" s="52"/>
+      <c r="C22" s="37"/>
       <c r="D22" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -1530,10 +1532,10 @@
       <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="54">
+      <c r="B23" s="39">
         <v>0.05</v>
       </c>
       <c r="C23" s="28"/>
@@ -1572,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="8"/>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="39">
         <v>0.1</v>
       </c>
       <c r="H24" s="33"/>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4699C9-F66D-48E1-9481-AC07CAB84031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E951CDBA-AEE0-4C40-AF2C-723773E628E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -450,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -563,6 +560,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1170,14 +1171,14 @@
         <v>0</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="56">
         <v>0.15</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="3">
+      <c r="H9" s="33"/>
+      <c r="I9" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1508,10 +1509,12 @@
       <c r="B22" s="27">
         <v>0.2</v>
       </c>
-      <c r="C22" s="37"/>
+      <c r="C22" s="37">
+        <v>5</v>
+      </c>
       <c r="D22" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="29" t="s">
@@ -1677,7 +1680,7 @@
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D28" s="16">
         <f>SUM(D19:D27)</f>
-        <v>3.18</v>
+        <v>4.18</v>
       </c>
     </row>
   </sheetData>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E951CDBA-AEE0-4C40-AF2C-723773E628E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67C5402-D107-4438-B66E-BA480EDD8BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -145,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,14 +235,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -447,7 +442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -492,16 +487,12 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -512,10 +503,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -561,10 +548,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,24 +874,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
-      <c r="F2" s="49" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="F2" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51"/>
-      <c r="K2" s="52" t="s">
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="47"/>
+      <c r="K2" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="54"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1036,16 +1020,16 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>0.1</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>10</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1064,96 +1048,96 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="29">
         <v>0.05</v>
       </c>
-      <c r="M6" s="32"/>
-      <c r="N6" s="31">
+      <c r="M6" s="31"/>
+      <c r="N6" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="33">
         <v>0.15</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>9.8000000000000007</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <f t="shared" si="0"/>
         <v>1.47</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="33">
         <v>0.1</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="30">
         <v>10</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="34" t="s">
+      <c r="K7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="35">
+      <c r="L7" s="33">
         <v>0.2</v>
       </c>
-      <c r="M7" s="32"/>
-      <c r="N7" s="31">
+      <c r="M7" s="31"/>
+      <c r="N7" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>0.1</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>7.4</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <f t="shared" si="0"/>
         <v>0.7400000000000001</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="29">
         <v>0.15</v>
       </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="31">
+      <c r="H8" s="34"/>
+      <c r="I8" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="29">
         <v>0.1</v>
       </c>
-      <c r="M8" s="32">
+      <c r="M8" s="31">
         <v>5.2</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="30">
         <f t="shared" si="2"/>
         <v>0.52</v>
       </c>
@@ -1171,14 +1155,14 @@
         <v>0</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="55" t="s">
+      <c r="F9" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="33">
         <v>0.15</v>
       </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="28">
+      <c r="H9" s="34"/>
+      <c r="I9" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1349,19 +1333,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1449,16 +1433,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="29">
         <v>0.15</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="30">
         <v>10</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="30">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>1.5</v>
       </c>
@@ -1469,30 +1453,30 @@
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>0.2</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="31">
         <v>8.4</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="30">
         <f t="shared" si="3"/>
         <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="35">
+      <c r="F21" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="33">
         <v>0.1</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="30">
         <v>8.52</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="30">
         <f t="shared" si="4"/>
         <v>0.85199999999999998</v>
       </c>
@@ -1509,7 +1493,7 @@
       <c r="B22" s="27">
         <v>0.2</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="35">
         <v>5</v>
       </c>
       <c r="D22" s="2">
@@ -1517,16 +1501,18 @@
         <v>1</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="29">
         <v>0.15</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="31">
+      <c r="H22" s="34">
+        <v>9</v>
+      </c>
+      <c r="I22" s="30">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.3499999999999999</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
@@ -1535,26 +1521,26 @@
       <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="39">
+      <c r="B23" s="29">
         <v>0.05</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E23" s="8"/>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="33">
         <v>0.1</v>
       </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="31">
+      <c r="H23" s="34"/>
+      <c r="I23" s="30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1577,16 +1563,18 @@
         <v>0</v>
       </c>
       <c r="E24" s="8"/>
-      <c r="F24" s="38" t="s">
+      <c r="F24" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="39">
+      <c r="G24" s="29">
         <v>0.1</v>
       </c>
-      <c r="H24" s="33"/>
-      <c r="I24" s="28">
+      <c r="H24" s="34">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="I24" s="30">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.87100000000000011</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -1607,14 +1595,14 @@
         <v>0</v>
       </c>
       <c r="E25" s="8"/>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="27">
         <v>0.1</v>
       </c>
-      <c r="H25" s="25"/>
-      <c r="I25" s="3">
+      <c r="H25" s="51"/>
+      <c r="I25" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1669,7 +1657,7 @@
       <c r="E27" s="8"/>
       <c r="I27" s="16">
         <f>SUM(I19:I26)</f>
-        <v>3.3519999999999999</v>
+        <v>5.5730000000000004</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67C5402-D107-4438-B66E-BA480EDD8BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E078483E-5D60-4A73-BC0A-E84B751E8FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -503,6 +500,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -548,7 +546,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -874,24 +871,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
-      <c r="F2" s="45" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="F2" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="47"/>
-      <c r="K2" s="48" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="48"/>
+      <c r="K2" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1161,10 +1158,12 @@
       <c r="G9" s="33">
         <v>0.15</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="34">
+        <v>9.7200000000000006</v>
+      </c>
       <c r="I9" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.458</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="19" t="s">
@@ -1260,7 +1259,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="16">
         <f>SUM(I4:I11)</f>
-        <v>4.0489999999999995</v>
+        <v>5.5069999999999997</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1333,19 +1332,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1601,7 +1600,7 @@
       <c r="G25" s="27">
         <v>0.1</v>
       </c>
-      <c r="H25" s="51"/>
+      <c r="H25" s="36"/>
       <c r="I25" s="2">
         <f t="shared" si="4"/>
         <v>0</v>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E078483E-5D60-4A73-BC0A-E84B751E8FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA8751D-0ECC-46CF-910D-A62B771CC270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -145,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +232,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -439,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -453,13 +461,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -473,13 +475,6 @@
     <xf numFmtId="9" fontId="9" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +539,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -871,24 +888,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="F2" s="46" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="40"/>
+      <c r="F2" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="48"/>
-      <c r="K2" s="49" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43"/>
+      <c r="K2" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="51"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="46"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -931,10 +948,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="16">
         <v>0.05</v>
       </c>
       <c r="C4" s="2">
@@ -945,10 +962,10 @@
         <v>0.48</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="16">
         <v>0.1</v>
       </c>
       <c r="H4" s="2">
@@ -959,10 +976,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="8"/>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="18">
+      <c r="L4" s="16">
         <v>0.15</v>
       </c>
       <c r="M4" s="10">
@@ -974,10 +991,10 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="22">
         <v>0.1</v>
       </c>
       <c r="C5" s="2">
@@ -988,10 +1005,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="22">
         <v>0.1</v>
       </c>
       <c r="H5" s="2">
@@ -1002,10 +1019,10 @@
         <v>0.9</v>
       </c>
       <c r="J5" s="8"/>
-      <c r="K5" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="27">
+      <c r="K5" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="22">
         <v>0.15</v>
       </c>
       <c r="M5" s="10">
@@ -1017,24 +1034,24 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="24">
         <v>0.1</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>10</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18">
+      <c r="F6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16">
         <v>0.15</v>
       </c>
       <c r="H6" s="2">
@@ -1045,146 +1062,146 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="24">
         <v>0.05</v>
       </c>
-      <c r="M6" s="31"/>
-      <c r="N6" s="30">
+      <c r="M6" s="26"/>
+      <c r="N6" s="25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="28">
         <v>0.15</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>9.8000000000000007</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <f t="shared" si="0"/>
         <v>1.47</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="28">
         <v>0.1</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="25">
         <v>10</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="25">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="28">
         <v>0.2</v>
       </c>
-      <c r="M7" s="31"/>
-      <c r="N7" s="30">
+      <c r="M7" s="26"/>
+      <c r="N7" s="25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="24">
         <v>0.1</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>7.4</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <f t="shared" si="0"/>
         <v>0.7400000000000001</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="24">
         <v>0.15</v>
       </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="30">
+      <c r="H8" s="29"/>
+      <c r="I8" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="24">
         <v>0.1</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="26">
         <v>5.2</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="25">
         <f t="shared" si="2"/>
         <v>0.52</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="48">
         <v>0.25</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3">
+      <c r="C9" s="49"/>
+      <c r="D9" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="28">
         <v>0.15</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="29">
         <v>9.7200000000000006</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="25">
         <f t="shared" si="1"/>
         <v>1.458</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="48">
         <v>0.15</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="M9" s="49">
+        <v>0</v>
+      </c>
+      <c r="N9" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="A10" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="20">
         <v>0.25</v>
       </c>
       <c r="C10" s="3"/>
@@ -1193,22 +1210,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="55">
         <v>0.1</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="3">
+      <c r="H10" s="56"/>
+      <c r="I10" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="21" t="s">
+      <c r="K10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="20">
         <v>0.2</v>
       </c>
       <c r="M10" s="3">
@@ -1221,17 +1238,17 @@
     </row>
     <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
-      <c r="B11" s="14"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="16">
+      <c r="D11" s="14">
         <f>SUM(D4:D10)</f>
         <v>4.6900000000000004</v>
       </c>
       <c r="E11" s="8"/>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="18">
         <v>0.15</v>
       </c>
       <c r="H11" s="3"/>
@@ -1243,7 +1260,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="16">
+      <c r="N11" s="14">
         <f>SUM(N4:N10)</f>
         <v>2.77</v>
       </c>
@@ -1257,7 +1274,7 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="16">
+      <c r="I12" s="14">
         <f>SUM(I4:I11)</f>
         <v>5.5069999999999997</v>
       </c>
@@ -1332,19 +1349,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1384,10 +1401,10 @@
       <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="16">
         <v>0.05</v>
       </c>
       <c r="C19" s="2">
@@ -1398,10 +1415,10 @@
         <v>0.5</v>
       </c>
       <c r="E19" s="8"/>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="16">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
@@ -1418,10 +1435,10 @@
       <c r="N19" s="8"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="A20" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="22">
         <v>0.1</v>
       </c>
       <c r="C20" s="2">
@@ -1432,16 +1449,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="24">
         <v>0.15</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="25">
         <v>10</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="25">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>1.5</v>
       </c>
@@ -1452,30 +1469,30 @@
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="24">
         <v>0.2</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="26">
         <v>8.4</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="25">
         <f t="shared" si="3"/>
         <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="33">
+      <c r="F21" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="28">
         <v>0.1</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="25">
         <v>8.52</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="25">
         <f t="shared" si="4"/>
         <v>0.85199999999999998</v>
       </c>
@@ -1486,13 +1503,13 @@
       <c r="N21" s="8"/>
     </row>
     <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="22">
         <v>0.2</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="30">
         <v>5</v>
       </c>
       <c r="D22" s="2">
@@ -1500,16 +1517,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="24">
         <v>0.15</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="29">
         <v>9</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="25">
         <f t="shared" si="4"/>
         <v>1.3499999999999999</v>
       </c>
@@ -1520,26 +1537,26 @@
       <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="24">
         <v>0.05</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30">
+      <c r="C23" s="25"/>
+      <c r="D23" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E23" s="8"/>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="28">
         <v>0.1</v>
       </c>
-      <c r="H23" s="34"/>
-      <c r="I23" s="30">
+      <c r="H23" s="29"/>
+      <c r="I23" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1550,28 +1567,28 @@
       <c r="N23" s="8"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="50">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="3">
+      <c r="C24" s="51"/>
+      <c r="D24" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E24" s="8"/>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="24">
         <v>0.1</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="29">
         <v>8.7100000000000009</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="25">
         <f t="shared" si="4"/>
         <v>0.87100000000000011</v>
       </c>
@@ -1582,25 +1599,25 @@
       <c r="N24" s="8"/>
     </row>
     <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="53">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="3">
+      <c r="C25" s="54"/>
+      <c r="D25" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E25" s="8"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="22">
         <v>0.1</v>
       </c>
-      <c r="H25" s="36"/>
+      <c r="H25" s="31"/>
       <c r="I25" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1612,10 +1629,10 @@
       <c r="N25" s="8"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="18">
         <v>0.2</v>
       </c>
       <c r="C26" s="3"/>
@@ -1624,10 +1641,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="8"/>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="20">
         <v>0.2</v>
       </c>
       <c r="H26" s="3"/>
@@ -1642,10 +1659,10 @@
       <c r="N26" s="8"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="20">
         <v>0.05</v>
       </c>
       <c r="C27" s="3"/>
@@ -1654,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="8"/>
-      <c r="I27" s="16">
+      <c r="I27" s="14">
         <f>SUM(I19:I26)</f>
         <v>5.5730000000000004</v>
       </c>
@@ -1665,7 +1682,7 @@
       <c r="N27" s="8"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D28" s="16">
+      <c r="D28" s="14">
         <f>SUM(D19:D27)</f>
         <v>4.18</v>
       </c>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA8751D-0ECC-46CF-910D-A62B771CC270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006198A1-D31F-4741-8FE1-8A9FA60AED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -496,51 +499,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -561,6 +519,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -888,24 +891,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="40"/>
-      <c r="F2" s="41" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
+      <c r="F2" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-      <c r="K2" s="44" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="53"/>
+      <c r="K2" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="46"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="56"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1068,10 +1071,12 @@
       <c r="L6" s="24">
         <v>0.05</v>
       </c>
-      <c r="M6" s="26"/>
+      <c r="M6" s="26">
+        <v>9.4</v>
+      </c>
       <c r="N6" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.47000000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -1157,14 +1162,14 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="48">
+      <c r="B9" s="33">
         <v>0.25</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49">
+      <c r="C9" s="34"/>
+      <c r="D9" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1183,16 +1188,14 @@
         <v>1.458</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="47" t="s">
+      <c r="K9" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="48">
+      <c r="L9" s="33">
         <v>0.15</v>
       </c>
-      <c r="M9" s="49">
-        <v>0</v>
-      </c>
-      <c r="N9" s="49">
+      <c r="M9" s="34"/>
+      <c r="N9" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1210,14 +1213,14 @@
         <v>0</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="40">
         <v>0.1</v>
       </c>
-      <c r="H10" s="56"/>
-      <c r="I10" s="49">
+      <c r="H10" s="41"/>
+      <c r="I10" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1228,9 +1231,7 @@
       <c r="L10" s="20">
         <v>0.2</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
+      <c r="M10" s="3"/>
       <c r="N10" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1262,7 +1263,7 @@
       <c r="M11" s="8"/>
       <c r="N11" s="14">
         <f>SUM(N4:N10)</f>
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1349,19 +1350,19 @@
       <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="44"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="47"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -1567,14 +1568,14 @@
       <c r="N23" s="8"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="50">
+      <c r="B24" s="35">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="49">
+      <c r="C24" s="36"/>
+      <c r="D24" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1599,14 +1600,14 @@
       <c r="N24" s="8"/>
     </row>
     <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="53">
+      <c r="B25" s="38">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="49">
+      <c r="C25" s="39"/>
+      <c r="D25" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006198A1-D31F-4741-8FE1-8A9FA60AED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7793CC-90CB-46C0-8CF0-6375C848738B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -1141,10 +1141,12 @@
       <c r="G8" s="24">
         <v>0.15</v>
       </c>
-      <c r="H8" s="29"/>
+      <c r="H8" s="29">
+        <v>8.9</v>
+      </c>
       <c r="I8" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.335</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="23" t="s">
@@ -1162,16 +1164,18 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="28">
         <v>0.25</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34">
+      <c r="C9" s="25">
+        <v>8.89</v>
+      </c>
+      <c r="D9" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.2225000000000001</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="27" t="s">
@@ -1225,14 +1229,14 @@
         <v>0</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="40">
         <v>0.2</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3">
+      <c r="M10" s="34"/>
+      <c r="N10" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1243,7 +1247,7 @@
       <c r="C11" s="9"/>
       <c r="D11" s="14">
         <f>SUM(D4:D10)</f>
-        <v>4.6900000000000004</v>
+        <v>6.9125000000000005</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="17" t="s">
@@ -1277,7 +1281,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="14">
         <f>SUM(I4:I11)</f>
-        <v>5.5069999999999997</v>
+        <v>6.8419999999999996</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7793CC-90CB-46C0-8CF0-6375C848738B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E1B2A8-B220-40C5-8EA4-1B883A587897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -148,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +240,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,6 +292,12 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -450,11 +461,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -514,13 +524,9 @@
     <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -566,6 +572,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -891,70 +898,70 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
-      <c r="F2" s="51" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="F2" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="53"/>
-      <c r="K2" s="54" t="s">
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="50"/>
+      <c r="K2" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="56"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="10"/>
+      <c r="K3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="15">
         <v>0.05</v>
       </c>
       <c r="C4" s="2">
@@ -964,11 +971,11 @@
         <f>+B4*C4</f>
         <v>0.48</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="15">
         <v>0.1</v>
       </c>
       <c r="H4" s="2">
@@ -978,14 +985,14 @@
         <f>+G4*H4</f>
         <v>1</v>
       </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="15" t="s">
+      <c r="J4" s="7"/>
+      <c r="K4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="15">
         <v>0.15</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>9</v>
       </c>
       <c r="N4" s="2">
@@ -994,10 +1001,10 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <v>0.1</v>
       </c>
       <c r="C5" s="2">
@@ -1007,11 +1014,11 @@
         <f t="shared" ref="D5:D10" si="0">+B5*C5</f>
         <v>1</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="21" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="21">
         <v>0.1</v>
       </c>
       <c r="H5" s="2">
@@ -1021,14 +1028,14 @@
         <f t="shared" ref="I5:I11" si="1">+G5*H5</f>
         <v>0.9</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="21" t="s">
+      <c r="J5" s="7"/>
+      <c r="K5" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="21">
         <v>0.15</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="9">
         <v>6</v>
       </c>
       <c r="N5" s="2">
@@ -1037,24 +1044,24 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>0.1</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>10</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="24">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="15" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <v>0.15</v>
       </c>
       <c r="H6" s="2">
@@ -1064,352 +1071,352 @@
         <f t="shared" si="1"/>
         <v>1.149</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="23" t="s">
+      <c r="J6" s="7"/>
+      <c r="K6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="23">
         <v>0.05</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="25">
         <v>9.4</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="24">
         <f t="shared" si="2"/>
         <v>0.47000000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0.15</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>9.8000000000000007</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <f t="shared" si="0"/>
         <v>1.47</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="27" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="27">
         <v>0.1</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="24">
         <v>10</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="27" t="s">
+      <c r="J7" s="7"/>
+      <c r="K7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="27">
         <v>0.2</v>
       </c>
-      <c r="M7" s="26"/>
-      <c r="N7" s="25">
+      <c r="M7" s="25"/>
+      <c r="N7" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>0.1</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="24">
         <v>7.4</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <f t="shared" si="0"/>
         <v>0.7400000000000001</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="23" t="s">
+      <c r="E8" s="7"/>
+      <c r="F8" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="23">
         <v>0.15</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
         <v>8.9</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="24">
         <f t="shared" si="1"/>
         <v>1.335</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="23" t="s">
+      <c r="J8" s="7"/>
+      <c r="K8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="23">
         <v>0.1</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="25">
         <v>5.2</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="24">
         <f t="shared" si="2"/>
         <v>0.52</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>0.25</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>8.89</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <f t="shared" si="0"/>
         <v>2.2225000000000001</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="27" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <v>0.15</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>9.7200000000000006</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="24">
         <f t="shared" si="1"/>
         <v>1.458</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="32" t="s">
+      <c r="J9" s="7"/>
+      <c r="K9" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="32">
         <v>0.15</v>
       </c>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34">
+      <c r="M9" s="33"/>
+      <c r="N9" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="38">
         <v>0.25</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3">
+      <c r="C10" s="33"/>
+      <c r="D10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="37" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="23">
         <v>0.1</v>
       </c>
-      <c r="H10" s="41"/>
-      <c r="I10" s="34">
+      <c r="H10" s="28"/>
+      <c r="I10" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="37" t="s">
+      <c r="J10" s="7"/>
+      <c r="K10" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="40">
+      <c r="L10" s="23">
         <v>0.2</v>
       </c>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34">
+      <c r="M10" s="24"/>
+      <c r="N10" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="14">
+    <row r="11" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="A11" s="7"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="54">
         <f>SUM(D4:D10)</f>
         <v>6.9125000000000005</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="32">
         <v>0.15</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3">
+      <c r="H11" s="33"/>
+      <c r="I11" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="14">
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="13">
         <f>SUM(N4:N10)</f>
         <v>3.24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="14">
+    <row r="12" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="54">
         <f>SUM(I4:I11)</f>
         <v>6.8419999999999996</v>
       </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="45" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="4" t="s">
+      <c r="E18" s="10"/>
+      <c r="F18" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="15">
         <v>0.05</v>
       </c>
       <c r="C19" s="2">
@@ -1419,11 +1426,11 @@
         <f>+B19*C19</f>
         <v>0.5</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="15" t="s">
+      <c r="E19" s="7"/>
+      <c r="F19" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="15">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
@@ -1433,17 +1440,17 @@
         <f>+G19*H19</f>
         <v>1</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="21">
         <v>0.1</v>
       </c>
       <c r="C20" s="2">
@@ -1453,243 +1460,245 @@
         <f t="shared" ref="D20:D27" si="3">+B20*C20</f>
         <v>1</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="23" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="23">
         <v>0.15</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="24">
         <v>10</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="24">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>1.5</v>
       </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="23">
         <v>0.2</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>8.4</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="24">
         <f t="shared" si="3"/>
         <v>1.6800000000000002</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="27" t="s">
+      <c r="E21" s="7"/>
+      <c r="F21" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="27">
         <v>0.1</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="24">
         <v>8.52</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="24">
         <f t="shared" si="4"/>
         <v>0.85199999999999998</v>
       </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="21">
         <v>0.2</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="29">
         <v>5</v>
       </c>
       <c r="D22" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="23" t="s">
+      <c r="E22" s="7"/>
+      <c r="F22" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="23">
         <v>0.15</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="28">
         <v>9</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="24">
         <f t="shared" si="4"/>
         <v>1.3499999999999999</v>
       </c>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="23">
         <v>0.05</v>
       </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25">
+      <c r="C23" s="24">
+        <v>10</v>
+      </c>
+      <c r="D23" s="24">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="H23" s="28"/>
+      <c r="I23" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="34">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="C24" s="35"/>
+      <c r="D24" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="28">
+      <c r="E24" s="7"/>
+      <c r="F24" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="23">
         <v>0.1</v>
       </c>
-      <c r="H23" s="29"/>
-      <c r="I23" s="25">
+      <c r="H24" s="28">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="I24" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="35">
+        <v>0.87100000000000011</v>
+      </c>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="37">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="34">
+      <c r="C25" s="35"/>
+      <c r="D25" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="24">
+      <c r="E25" s="7"/>
+      <c r="F25" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="21">
         <v>0.1</v>
       </c>
-      <c r="H24" s="29">
-        <v>8.7100000000000009</v>
-      </c>
-      <c r="I24" s="25">
-        <f t="shared" si="4"/>
-        <v>0.87100000000000011</v>
-      </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="38">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H25" s="31"/>
+      <c r="H25" s="30"/>
       <c r="I25" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="17">
         <v>0.2</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3">
+      <c r="C26" s="35"/>
+      <c r="D26" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="19" t="s">
+      <c r="E26" s="7"/>
+      <c r="F26" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="38">
         <v>0.2</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3">
+      <c r="H26" s="33"/>
+      <c r="I26" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-    </row>
-    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="19">
         <v>0.05</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3">
+      <c r="C27" s="35"/>
+      <c r="D27" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="I27" s="14">
+      <c r="E27" s="7"/>
+      <c r="I27" s="54">
         <f>SUM(I19:I26)</f>
         <v>5.5730000000000004</v>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <f>SUM(D19:D27)</f>
-        <v>4.18</v>
+        <v>4.68</v>
       </c>
     </row>
   </sheetData>

--- a/Ciclo 01/Cuadro de notas.xlsx
+++ b/Ciclo 01/Cuadro de notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E1B2A8-B220-40C5-8EA4-1B883A587897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE91FFE0-BF87-4AB4-AF63-33A17F24C224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -145,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,14 +234,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="16"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -461,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -475,7 +467,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -508,23 +499,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -572,7 +558,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -898,24 +883,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
-      <c r="F2" s="48" t="s">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="F2" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="50"/>
-      <c r="K2" s="51" t="s">
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="46"/>
+      <c r="K2" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="53"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -958,10 +943,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>0.05</v>
       </c>
       <c r="C4" s="2">
@@ -972,10 +957,10 @@
         <v>0.48</v>
       </c>
       <c r="E4" s="7"/>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="14">
         <v>0.1</v>
       </c>
       <c r="H4" s="2">
@@ -986,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="7"/>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="14">
         <v>0.15</v>
       </c>
       <c r="M4" s="9">
@@ -1001,10 +986,10 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <v>0.1</v>
       </c>
       <c r="C5" s="2">
@@ -1015,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="20">
         <v>0.1</v>
       </c>
       <c r="H5" s="2">
@@ -1029,10 +1014,10 @@
         <v>0.9</v>
       </c>
       <c r="J5" s="7"/>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="20">
         <v>0.15</v>
       </c>
       <c r="M5" s="9">
@@ -1044,24 +1029,24 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="22">
         <v>0.1</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>10</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <v>0.15</v>
       </c>
       <c r="H6" s="2">
@@ -1072,178 +1057,182 @@
         <v>1.149</v>
       </c>
       <c r="J6" s="7"/>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="22">
         <v>0.05</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="24">
         <v>9.4</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N6" s="23">
         <f t="shared" si="2"/>
         <v>0.47000000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <v>0.15</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>9.8000000000000007</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <f t="shared" si="0"/>
         <v>1.47</v>
       </c>
       <c r="E7" s="7"/>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="26">
         <v>0.1</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <v>10</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="23">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="26">
         <v>0.2</v>
       </c>
-      <c r="M7" s="25"/>
-      <c r="N7" s="24">
+      <c r="M7" s="24"/>
+      <c r="N7" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <v>0.1</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>7.4</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <f t="shared" si="0"/>
         <v>0.7400000000000001</v>
       </c>
       <c r="E8" s="7"/>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>0.15</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <v>8.9</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="23">
         <f t="shared" si="1"/>
         <v>1.335</v>
       </c>
       <c r="J8" s="7"/>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="22">
         <v>0.1</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="24">
         <v>5.2</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="23">
         <f t="shared" si="2"/>
         <v>0.52</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="26">
         <v>0.25</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <v>8.89</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <f t="shared" si="0"/>
         <v>2.2225000000000001</v>
       </c>
       <c r="E9" s="7"/>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="26">
         <v>0.15</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <v>9.7200000000000006</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="23">
         <f t="shared" si="1"/>
         <v>1.458</v>
       </c>
       <c r="J9" s="7"/>
-      <c r="K9" s="31" t="s">
+      <c r="K9" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="26">
         <v>0.15</v>
       </c>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33">
+      <c r="M9" s="23">
+        <v>10</v>
+      </c>
+      <c r="N9" s="23">
         <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="38">
+      <c r="B10" s="22">
         <v>0.25</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33">
+      <c r="C10" s="23">
+        <v>7.59</v>
+      </c>
+      <c r="D10" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.8975</v>
       </c>
       <c r="E10" s="7"/>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="22">
         <v>0.1</v>
       </c>
-      <c r="H10" s="28"/>
-      <c r="I10" s="24">
+      <c r="H10" s="27"/>
+      <c r="I10" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J10" s="7"/>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="22">
         <v>0.2</v>
       </c>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24">
+      <c r="M10" s="23"/>
+      <c r="N10" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1252,19 +1241,19 @@
       <c r="A11" s="7"/>
       <c r="B11" s="12"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="54">
+      <c r="D11" s="31">
         <f>SUM(D4:D10)</f>
-        <v>6.9125000000000005</v>
+        <v>8.81</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="26">
         <v>0.15</v>
       </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33">
+      <c r="H11" s="23"/>
+      <c r="I11" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1272,9 +1261,9 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="13">
+      <c r="N11" s="31">
         <f>SUM(N4:N10)</f>
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21" x14ac:dyDescent="0.35">
@@ -1286,7 +1275,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="54">
+      <c r="I12" s="31">
         <f>SUM(I4:I11)</f>
         <v>6.8419999999999996</v>
       </c>
@@ -1361,19 +1350,19 @@
       <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="41"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -1413,10 +1402,10 @@
       <c r="N18" s="10"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>0.05</v>
       </c>
       <c r="C19" s="2">
@@ -1427,10 +1416,10 @@
         <v>0.5</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="14">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
@@ -1447,10 +1436,10 @@
       <c r="N19" s="7"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>0.1</v>
       </c>
       <c r="C20" s="2">
@@ -1461,16 +1450,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="7"/>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="22">
         <v>0.15</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="23">
         <v>10</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="23">
         <f t="shared" ref="I20:I26" si="4">+G20*H20</f>
         <v>1.5</v>
       </c>
@@ -1481,30 +1470,30 @@
       <c r="N20" s="7"/>
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <v>0.2</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>8.4</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <f t="shared" si="3"/>
         <v>1.6800000000000002</v>
       </c>
       <c r="E21" s="7"/>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="26">
         <v>0.1</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="23">
         <v>8.52</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="23">
         <f t="shared" si="4"/>
         <v>0.85199999999999998</v>
       </c>
@@ -1515,13 +1504,13 @@
       <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>0.2</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="28">
         <v>5</v>
       </c>
       <c r="D22" s="2">
@@ -1529,16 +1518,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="7"/>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="22">
         <v>0.15</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="27">
         <v>9</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="23">
         <f t="shared" si="4"/>
         <v>1.3499999999999999</v>
       </c>
@@ -1549,30 +1538,32 @@
       <c r="N22" s="7"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="22">
         <v>0.05</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="23">
         <v>10</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="23">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="E23" s="7"/>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="26">
         <v>0.1</v>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="24">
+      <c r="H23" s="27">
+        <v>9</v>
+      </c>
+      <c r="I23" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -1581,28 +1572,30 @@
       <c r="N23" s="7"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="34">
+      <c r="B24" s="32">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="33">
+      <c r="C24" s="33">
+        <v>9</v>
+      </c>
+      <c r="D24" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.67499999999999993</v>
       </c>
       <c r="E24" s="7"/>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="22">
         <v>0.1</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="27">
         <v>8.7100000000000009</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="23">
         <f t="shared" si="4"/>
         <v>0.87100000000000011</v>
       </c>
@@ -1613,28 +1606,32 @@
       <c r="N24" s="7"/>
     </row>
     <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="34">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="33">
+      <c r="C25" s="33">
+        <v>9</v>
+      </c>
+      <c r="D25" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.67499999999999993</v>
       </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="20">
         <v>0.1</v>
       </c>
-      <c r="H25" s="30"/>
+      <c r="H25" s="27">
+        <v>10</v>
+      </c>
       <c r="I25" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -1643,26 +1640,26 @@
       <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <v>0.2</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="33">
+      <c r="C26" s="30"/>
+      <c r="D26" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E26" s="7"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="38">
+      <c r="G26" s="22">
         <v>0.2</v>
       </c>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33">
+      <c r="H26" s="23"/>
+      <c r="I26" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1673,21 +1670,21 @@
       <c r="N26" s="7"/>
     </row>
     <row r="27" spans="1:14" ht="21" x14ac:dyDescent="0.35">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="18">
         <v>0.05</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="33">
+      <c r="C27" s="30"/>
+      <c r="D27" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E27" s="7"/>
-      <c r="I27" s="54">
+      <c r="I27" s="31">
         <f>SUM(I19:I26)</f>
-        <v>5.5730000000000004</v>
+        <v>7.4730000000000008</v>
       </c>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
@@ -1695,10 +1692,10 @@
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D28" s="13">
+    <row r="28" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="D28" s="31">
         <f>SUM(D19:D27)</f>
-        <v>4.68</v>
+        <v>6.0299999999999994</v>
       </c>
     </row>
   </sheetData>
